--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
@@ -166,15 +166,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,6 +186,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -565,7 +568,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -580,7 +583,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -602,22 +605,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -658,220 +661,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -896,7 +899,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.5703125" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -911,7 +914,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -933,22 +936,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -989,220 +992,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1227,7 +1230,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.28515625" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -1242,7 +1245,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -1264,22 +1267,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1320,220 +1323,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1558,7 +1561,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2022,7 +2025,7 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -2030,20 +2033,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Нечеткий MoSCoW — расчеты (коллективное решение)</t>
+          <t>Нечеткий MoSCoW - расчеты (коллективное решение, метод взвешенной средней)</t>
         </is>
       </c>
     </row>
@@ -2078,10 +2081,10 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2091,10 +2094,10 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2104,23 +2107,23 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2150,7 +2153,7 @@
           <t>a (редукция типа CLTR)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2160,7 +2163,7 @@
           <t>alpha (уровень альфа-среза)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="17" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2293,57 +2296,57 @@
       <c r="A20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>12.83</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="J20" s="14" t="n">
+      <c r="J20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="17" t="n">
         <v>14.13</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="L20" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="M20" s="14" t="n">
+      <c r="M20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="N20" s="14" t="n">
+      <c r="N20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="O20" s="14" t="n">
+      <c r="O20" s="17" t="n">
         <v>20.83</v>
       </c>
-      <c r="P20" s="14" t="n">
+      <c r="P20" s="17" t="n">
         <v>25.5</v>
       </c>
-      <c r="Q20" s="14" t="n">
+      <c r="Q20" s="17" t="n">
         <v>23.16</v>
       </c>
-      <c r="R20" s="14" t="n">
+      <c r="R20" s="17" t="n">
         <v>23.16</v>
       </c>
     </row>
@@ -2351,57 +2354,57 @@
       <c r="A21" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>11.04</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="17" t="n">
         <v>24.57</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="17" t="n">
         <v>12.97</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I21" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="J21" s="14" t="n">
+      <c r="J21" s="17" t="n">
         <v>24.31</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="17" t="n">
         <v>12.2</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" s="17" t="n">
         <v>19.12</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="17" t="n">
         <v>23.54</v>
       </c>
-      <c r="N21" s="14" t="n">
+      <c r="N21" s="17" t="n">
         <v>24.41</v>
       </c>
-      <c r="O21" s="14" t="n">
+      <c r="O21" s="17" t="n">
         <v>17.74</v>
       </c>
-      <c r="P21" s="14" t="n">
+      <c r="P21" s="17" t="n">
         <v>23.71</v>
       </c>
-      <c r="Q21" s="14" t="n">
+      <c r="Q21" s="17" t="n">
         <v>20.73</v>
       </c>
-      <c r="R21" s="14" t="n">
+      <c r="R21" s="17" t="n">
         <v>23.16</v>
       </c>
     </row>
@@ -2409,57 +2412,57 @@
       <c r="A22" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>7.44</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="17" t="n">
         <v>22.71</v>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="G22" s="17" t="n">
         <v>8.94</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="J22" s="14" t="n">
+      <c r="J22" s="17" t="n">
         <v>21.93</v>
       </c>
-      <c r="K22" s="14" t="n">
+      <c r="K22" s="17" t="n">
         <v>8.34</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" s="17" t="n">
         <v>12.38</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="N22" s="14" t="n">
+      <c r="N22" s="17" t="n">
         <v>22.24</v>
       </c>
-      <c r="O22" s="14" t="n">
+      <c r="O22" s="17" t="n">
         <v>11.57</v>
       </c>
-      <c r="P22" s="14" t="n">
+      <c r="P22" s="17" t="n">
         <v>20.15</v>
       </c>
-      <c r="Q22" s="14" t="n">
+      <c r="Q22" s="17" t="n">
         <v>15.86</v>
       </c>
-      <c r="R22" s="14" t="n">
+      <c r="R22" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2467,57 +2470,57 @@
       <c r="A23" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>4.28</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F23" s="17" t="n">
         <v>17.86</v>
       </c>
-      <c r="G23" s="14" t="n">
+      <c r="G23" s="17" t="n">
         <v>5.46</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I23" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="J23" s="17" t="n">
         <v>17.34</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="17" t="n">
         <v>4.99</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="M23" s="14" t="n">
+      <c r="M23" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="N23" s="14" t="n">
+      <c r="N23" s="17" t="n">
         <v>17.55</v>
       </c>
-      <c r="O23" s="14" t="n">
+      <c r="O23" s="17" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="P23" s="14" t="n">
+      <c r="P23" s="17" t="n">
         <v>16.29</v>
       </c>
-      <c r="Q23" s="14" t="n">
+      <c r="Q23" s="17" t="n">
         <v>12.96</v>
       </c>
-      <c r="R23" s="14" t="n">
+      <c r="R23" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2525,57 +2528,57 @@
       <c r="A24" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14" t="n">
+      <c r="C24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17" t="n">
         <v>5.61</v>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="14" t="n">
+      <c r="G24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="n">
         <v>3.81</v>
       </c>
-      <c r="K24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="14" t="n">
+      <c r="K24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="17" t="n">
         <v>4.53</v>
       </c>
-      <c r="O24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="14" t="n">
+      <c r="O24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="17" t="n">
         <v>0.91</v>
       </c>
-      <c r="Q24" s="14" t="n">
+      <c r="Q24" s="17" t="n">
         <v>0.46</v>
       </c>
-      <c r="R24" s="14" t="n">
+      <c r="R24" s="17" t="n">
         <v>15.86</v>
       </c>
     </row>
@@ -2583,57 +2586,57 @@
       <c r="A25" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>4.96</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="17" t="n">
         <v>19.82</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="17" t="n">
         <v>6.19</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="J25" s="17" t="n">
         <v>19.04</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="17" t="n">
         <v>5.7</v>
       </c>
-      <c r="L25" s="14" t="n">
+      <c r="L25" s="17" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="M25" s="14" t="n">
+      <c r="M25" s="17" t="n">
         <v>16.82</v>
       </c>
-      <c r="N25" s="14" t="n">
+      <c r="N25" s="17" t="n">
         <v>19.35</v>
       </c>
-      <c r="O25" s="14" t="n">
+      <c r="O25" s="17" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="P25" s="14" t="n">
+      <c r="P25" s="17" t="n">
         <v>17.33</v>
       </c>
-      <c r="Q25" s="14" t="n">
+      <c r="Q25" s="17" t="n">
         <v>13.19</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="17" t="n">
         <v>13.19</v>
       </c>
     </row>
@@ -2641,57 +2644,57 @@
       <c r="A26" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>6.76</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="17" t="n">
         <v>17.94</v>
       </c>
-      <c r="G26" s="14" t="n">
+      <c r="G26" s="17" t="n">
         <v>7.98</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I26" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="J26" s="14" t="n">
+      <c r="J26" s="17" t="n">
         <v>17.08</v>
       </c>
-      <c r="K26" s="14" t="n">
+      <c r="K26" s="17" t="n">
         <v>7.49</v>
       </c>
-      <c r="L26" s="14" t="n">
+      <c r="L26" s="17" t="n">
         <v>11.62</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="M26" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="N26" s="14" t="n">
+      <c r="N26" s="17" t="n">
         <v>17.42</v>
       </c>
-      <c r="O26" s="14" t="n">
+      <c r="O26" s="17" t="n">
         <v>10.79</v>
       </c>
-      <c r="P26" s="14" t="n">
+      <c r="P26" s="17" t="n">
         <v>15.52</v>
       </c>
-      <c r="Q26" s="14" t="n">
+      <c r="Q26" s="17" t="n">
         <v>13.15</v>
       </c>
-      <c r="R26" s="14" t="n">
+      <c r="R26" s="17" t="n">
         <v>13.15</v>
       </c>
     </row>
@@ -2699,57 +2702,57 @@
       <c r="A27" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>4.96</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="17" t="n">
         <v>17.01</v>
       </c>
-      <c r="G27" s="14" t="n">
+      <c r="G27" s="17" t="n">
         <v>5.96</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H27" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="17" t="n">
         <v>15.89</v>
       </c>
-      <c r="K27" s="14" t="n">
+      <c r="K27" s="17" t="n">
         <v>5.56</v>
       </c>
-      <c r="L27" s="14" t="n">
+      <c r="L27" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="M27" s="14" t="n">
+      <c r="M27" s="17" t="n">
         <v>13.09</v>
       </c>
-      <c r="N27" s="14" t="n">
+      <c r="N27" s="17" t="n">
         <v>16.34</v>
       </c>
-      <c r="O27" s="14" t="n">
+      <c r="O27" s="17" t="n">
         <v>7.71</v>
       </c>
-      <c r="P27" s="14" t="n">
+      <c r="P27" s="17" t="n">
         <v>13.74</v>
       </c>
-      <c r="Q27" s="14" t="n">
+      <c r="Q27" s="17" t="n">
         <v>10.72</v>
       </c>
-      <c r="R27" s="14" t="n">
+      <c r="R27" s="17" t="n">
         <v>10.72</v>
       </c>
     </row>
@@ -2757,57 +2760,57 @@
       <c r="A28" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="14" t="n">
+      <c r="C28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="17" t="n">
         <v>14.04</v>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="17" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="I28" s="14" t="n">
+      <c r="I28" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="J28" s="14" t="n">
+      <c r="J28" s="17" t="n">
         <v>13.26</v>
       </c>
-      <c r="K28" s="14" t="n">
+      <c r="K28" s="17" t="n">
         <v>0.41</v>
       </c>
-      <c r="L28" s="14" t="n">
+      <c r="L28" s="17" t="n">
         <v>4.95</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="M28" s="17" t="n">
         <v>11.22</v>
       </c>
-      <c r="N28" s="14" t="n">
+      <c r="N28" s="17" t="n">
         <v>13.57</v>
       </c>
-      <c r="O28" s="14" t="n">
+      <c r="O28" s="17" t="n">
         <v>4.04</v>
       </c>
-      <c r="P28" s="14" t="n">
+      <c r="P28" s="17" t="n">
         <v>11.69</v>
       </c>
-      <c r="Q28" s="14" t="n">
+      <c r="Q28" s="17" t="n">
         <v>7.87</v>
       </c>
-      <c r="R28" s="14" t="n">
+      <c r="R28" s="17" t="n">
         <v>10.72</v>
       </c>
     </row>
@@ -2815,57 +2818,57 @@
       <c r="A29" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>2.48</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="17" t="n">
         <v>11.31</v>
       </c>
-      <c r="G29" s="14" t="n">
+      <c r="G29" s="17" t="n">
         <v>2.98</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="I29" s="14" t="n">
+      <c r="I29" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="J29" s="14" t="n">
+      <c r="J29" s="17" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="17" t="n">
         <v>2.78</v>
       </c>
-      <c r="L29" s="14" t="n">
+      <c r="L29" s="17" t="n">
         <v>4.12</v>
       </c>
-      <c r="M29" s="14" t="n">
+      <c r="M29" s="17" t="n">
         <v>6.54</v>
       </c>
-      <c r="N29" s="14" t="n">
+      <c r="N29" s="17" t="n">
         <v>10.44</v>
       </c>
-      <c r="O29" s="14" t="n">
+      <c r="O29" s="17" t="n">
         <v>3.85</v>
       </c>
-      <c r="P29" s="14" t="n">
+      <c r="P29" s="17" t="n">
         <v>7.32</v>
       </c>
-      <c r="Q29" s="14" t="n">
+      <c r="Q29" s="17" t="n">
         <v>5.58</v>
       </c>
-      <c r="R29" s="14" t="n">
+      <c r="R29" s="17" t="n">
         <v>5.58</v>
       </c>
     </row>
@@ -2990,57 +2993,57 @@
       <c r="A34" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="17" t="n">
         <v>10.91</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="17" t="n">
         <v>24.5</v>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G34" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H34" s="14" t="n">
+      <c r="H34" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="I34" s="14" t="n">
+      <c r="I34" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="J34" s="14" t="n">
+      <c r="J34" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="K34" s="14" t="n">
+      <c r="K34" s="17" t="n">
         <v>12.16</v>
       </c>
-      <c r="L34" s="14" t="n">
+      <c r="L34" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="N34" s="14" t="n">
+      <c r="N34" s="17" t="n">
         <v>24.2</v>
       </c>
-      <c r="O34" s="14" t="n">
+      <c r="O34" s="17" t="n">
         <v>18.43</v>
       </c>
-      <c r="P34" s="14" t="n">
+      <c r="P34" s="17" t="n">
         <v>23.24</v>
       </c>
-      <c r="Q34" s="14" t="n">
+      <c r="Q34" s="17" t="n">
         <v>20.84</v>
       </c>
-      <c r="R34" s="14" t="n">
+      <c r="R34" s="17" t="n">
         <v>20.84</v>
       </c>
     </row>
@@ -3048,57 +3051,57 @@
       <c r="A35" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="17" t="n">
         <v>10.91</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E35" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="17" t="n">
         <v>24.5</v>
       </c>
-      <c r="G35" s="14" t="n">
+      <c r="G35" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="I35" s="14" t="n">
+      <c r="I35" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="J35" s="14" t="n">
+      <c r="J35" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="K35" s="14" t="n">
+      <c r="K35" s="17" t="n">
         <v>12.16</v>
       </c>
-      <c r="L35" s="14" t="n">
+      <c r="L35" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="M35" s="14" t="n">
+      <c r="M35" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="N35" s="14" t="n">
+      <c r="N35" s="17" t="n">
         <v>24.2</v>
       </c>
-      <c r="O35" s="14" t="n">
+      <c r="O35" s="17" t="n">
         <v>18.43</v>
       </c>
-      <c r="P35" s="14" t="n">
+      <c r="P35" s="17" t="n">
         <v>23.24</v>
       </c>
-      <c r="Q35" s="14" t="n">
+      <c r="Q35" s="17" t="n">
         <v>20.84</v>
       </c>
-      <c r="R35" s="14" t="n">
+      <c r="R35" s="17" t="n">
         <v>20.84</v>
       </c>
     </row>
@@ -3106,57 +3109,57 @@
       <c r="A36" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C36" s="17" t="n">
         <v>7.3</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="E36" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="F36" s="14" t="n">
+      <c r="F36" s="17" t="n">
         <v>22.64</v>
       </c>
-      <c r="G36" s="14" t="n">
+      <c r="G36" s="17" t="n">
         <v>8.960000000000001</v>
       </c>
-      <c r="H36" s="14" t="n">
+      <c r="H36" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="I36" s="14" t="n">
+      <c r="I36" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="J36" s="14" t="n">
+      <c r="J36" s="17" t="n">
         <v>21.62</v>
       </c>
-      <c r="K36" s="14" t="n">
+      <c r="K36" s="17" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L36" s="14" t="n">
+      <c r="L36" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="M36" s="14" t="n">
+      <c r="M36" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="N36" s="14" t="n">
+      <c r="N36" s="17" t="n">
         <v>22.03</v>
       </c>
-      <c r="O36" s="14" t="n">
+      <c r="O36" s="17" t="n">
         <v>12.25</v>
       </c>
-      <c r="P36" s="14" t="n">
+      <c r="P36" s="17" t="n">
         <v>19.68</v>
       </c>
-      <c r="Q36" s="14" t="n">
+      <c r="Q36" s="17" t="n">
         <v>15.96</v>
       </c>
-      <c r="R36" s="14" t="n">
+      <c r="R36" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3164,57 +3167,57 @@
       <c r="A37" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="17" t="n">
         <v>5.66</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E37" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="F37" s="14" t="n">
+      <c r="F37" s="17" t="n">
         <v>19.68</v>
       </c>
-      <c r="G37" s="14" t="n">
+      <c r="G37" s="17" t="n">
         <v>7.03</v>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="H37" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="I37" s="14" t="n">
+      <c r="I37" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="J37" s="14" t="n">
+      <c r="J37" s="17" t="n">
         <v>18.85</v>
       </c>
-      <c r="K37" s="14" t="n">
+      <c r="K37" s="17" t="n">
         <v>6.48</v>
       </c>
-      <c r="L37" s="14" t="n">
+      <c r="L37" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="M37" s="14" t="n">
+      <c r="M37" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="N37" s="14" t="n">
+      <c r="N37" s="17" t="n">
         <v>19.18</v>
       </c>
-      <c r="O37" s="14" t="n">
+      <c r="O37" s="17" t="n">
         <v>10.82</v>
       </c>
-      <c r="P37" s="14" t="n">
+      <c r="P37" s="17" t="n">
         <v>17.32</v>
       </c>
-      <c r="Q37" s="14" t="n">
+      <c r="Q37" s="17" t="n">
         <v>14.07</v>
       </c>
-      <c r="R37" s="14" t="n">
+      <c r="R37" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3222,57 +3225,57 @@
       <c r="A38" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="14" t="n">
+      <c r="C38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E38" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="F38" s="14" t="n">
+      <c r="F38" s="17" t="n">
         <v>7.7</v>
       </c>
-      <c r="G38" s="14" t="n">
+      <c r="G38" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="I38" s="14" t="n">
+      <c r="I38" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="J38" s="14" t="n">
+      <c r="J38" s="17" t="n">
         <v>6.11</v>
       </c>
-      <c r="K38" s="14" t="n">
+      <c r="K38" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="L38" s="14" t="n">
+      <c r="L38" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="M38" s="14" t="n">
+      <c r="M38" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="N38" s="14" t="n">
+      <c r="N38" s="17" t="n">
         <v>6.75</v>
       </c>
-      <c r="O38" s="14" t="n">
+      <c r="O38" s="17" t="n">
         <v>0.89</v>
       </c>
-      <c r="P38" s="14" t="n">
+      <c r="P38" s="17" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="17" t="n">
         <v>2.17</v>
       </c>
-      <c r="R38" s="14" t="n">
+      <c r="R38" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3280,57 +3283,57 @@
       <c r="A39" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>6.33</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E39" s="17" t="n">
         <v>17.7</v>
       </c>
-      <c r="F39" s="14" t="n">
+      <c r="F39" s="17" t="n">
         <v>21.64</v>
       </c>
-      <c r="G39" s="14" t="n">
+      <c r="G39" s="17" t="n">
         <v>7.76</v>
       </c>
-      <c r="H39" s="14" t="n">
+      <c r="H39" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="I39" s="14" t="n">
+      <c r="I39" s="17" t="n">
         <v>17.7</v>
       </c>
-      <c r="J39" s="14" t="n">
+      <c r="J39" s="17" t="n">
         <v>20.55</v>
       </c>
-      <c r="K39" s="14" t="n">
+      <c r="K39" s="17" t="n">
         <v>7.19</v>
       </c>
-      <c r="L39" s="14" t="n">
+      <c r="L39" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="M39" s="14" t="n">
+      <c r="M39" s="17" t="n">
         <v>17.7</v>
       </c>
-      <c r="N39" s="14" t="n">
+      <c r="N39" s="17" t="n">
         <v>20.99</v>
       </c>
-      <c r="O39" s="14" t="n">
+      <c r="O39" s="17" t="n">
         <v>10.24</v>
       </c>
-      <c r="P39" s="14" t="n">
+      <c r="P39" s="17" t="n">
         <v>18.36</v>
       </c>
-      <c r="Q39" s="14" t="n">
+      <c r="Q39" s="17" t="n">
         <v>14.3</v>
       </c>
-      <c r="R39" s="14" t="n">
+      <c r="R39" s="17" t="n">
         <v>14.3</v>
       </c>
     </row>
@@ -3338,57 +3341,57 @@
       <c r="A40" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="17" t="n">
         <v>6.62</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="17" t="n">
         <v>12.5</v>
       </c>
-      <c r="E40" s="14" t="n">
+      <c r="E40" s="17" t="n">
         <v>14.5</v>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="17" t="n">
         <v>17.87</v>
       </c>
-      <c r="G40" s="14" t="n">
+      <c r="G40" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="17" t="n">
         <v>12.5</v>
       </c>
-      <c r="I40" s="14" t="n">
+      <c r="I40" s="17" t="n">
         <v>14.5</v>
       </c>
-      <c r="J40" s="14" t="n">
+      <c r="J40" s="17" t="n">
         <v>16.77</v>
       </c>
-      <c r="K40" s="14" t="n">
+      <c r="K40" s="17" t="n">
         <v>7.45</v>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="17" t="n">
         <v>12.5</v>
       </c>
-      <c r="M40" s="14" t="n">
+      <c r="M40" s="17" t="n">
         <v>14.5</v>
       </c>
-      <c r="N40" s="14" t="n">
+      <c r="N40" s="17" t="n">
         <v>17.21</v>
       </c>
-      <c r="O40" s="14" t="n">
+      <c r="O40" s="17" t="n">
         <v>11.49</v>
       </c>
-      <c r="P40" s="14" t="n">
+      <c r="P40" s="17" t="n">
         <v>15.04</v>
       </c>
-      <c r="Q40" s="14" t="n">
+      <c r="Q40" s="17" t="n">
         <v>13.27</v>
       </c>
-      <c r="R40" s="14" t="n">
+      <c r="R40" s="17" t="n">
         <v>13.27</v>
       </c>
     </row>
@@ -3396,57 +3399,57 @@
       <c r="A41" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="19" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C41" s="17" t="n">
         <v>4.83</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="E41" s="14" t="n">
+      <c r="E41" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="F41" s="14" t="n">
+      <c r="F41" s="17" t="n">
         <v>16.94</v>
       </c>
-      <c r="G41" s="14" t="n">
+      <c r="G41" s="17" t="n">
         <v>5.98</v>
       </c>
-      <c r="H41" s="14" t="n">
+      <c r="H41" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="J41" s="14" t="n">
+      <c r="J41" s="17" t="n">
         <v>15.59</v>
       </c>
-      <c r="K41" s="14" t="n">
+      <c r="K41" s="17" t="n">
         <v>5.52</v>
       </c>
-      <c r="L41" s="14" t="n">
+      <c r="L41" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="M41" s="14" t="n">
+      <c r="M41" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="N41" s="14" t="n">
+      <c r="N41" s="17" t="n">
         <v>16.13</v>
       </c>
-      <c r="O41" s="14" t="n">
+      <c r="O41" s="17" t="n">
         <v>8.4</v>
       </c>
-      <c r="P41" s="14" t="n">
+      <c r="P41" s="17" t="n">
         <v>13.26</v>
       </c>
-      <c r="Q41" s="14" t="n">
+      <c r="Q41" s="17" t="n">
         <v>10.83</v>
       </c>
-      <c r="R41" s="14" t="n">
+      <c r="R41" s="17" t="n">
         <v>10.83</v>
       </c>
     </row>
@@ -3454,57 +3457,57 @@
       <c r="A42" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B42" s="19" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="17" t="n">
         <v>1.38</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E42" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="F42" s="14" t="n">
+      <c r="F42" s="17" t="n">
         <v>15.86</v>
       </c>
-      <c r="G42" s="14" t="n">
+      <c r="G42" s="17" t="n">
         <v>2.26</v>
       </c>
-      <c r="H42" s="14" t="n">
+      <c r="H42" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="I42" s="14" t="n">
+      <c r="I42" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="J42" s="14" t="n">
+      <c r="J42" s="17" t="n">
         <v>14.77</v>
       </c>
-      <c r="K42" s="14" t="n">
+      <c r="K42" s="17" t="n">
         <v>1.91</v>
       </c>
-      <c r="L42" s="14" t="n">
+      <c r="L42" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="N42" s="14" t="n">
+      <c r="N42" s="17" t="n">
         <v>15.21</v>
       </c>
-      <c r="O42" s="14" t="n">
+      <c r="O42" s="17" t="n">
         <v>5.22</v>
       </c>
-      <c r="P42" s="14" t="n">
+      <c r="P42" s="17" t="n">
         <v>12.72</v>
       </c>
-      <c r="Q42" s="14" t="n">
+      <c r="Q42" s="17" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="R42" s="14" t="n">
+      <c r="R42" s="17" t="n">
         <v>10.83</v>
       </c>
     </row>
@@ -3512,57 +3515,57 @@
       <c r="A43" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C43" s="17" t="n">
         <v>2.48</v>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="17" t="n">
         <v>5.22</v>
       </c>
-      <c r="E43" s="14" t="n">
+      <c r="E43" s="17" t="n">
         <v>9.18</v>
       </c>
-      <c r="F43" s="14" t="n">
+      <c r="F43" s="17" t="n">
         <v>13.4</v>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="G43" s="17" t="n">
         <v>3.06</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="17" t="n">
         <v>5.22</v>
       </c>
-      <c r="I43" s="14" t="n">
+      <c r="I43" s="17" t="n">
         <v>9.18</v>
       </c>
-      <c r="J43" s="14" t="n">
+      <c r="J43" s="17" t="n">
         <v>12.14</v>
       </c>
-      <c r="K43" s="14" t="n">
+      <c r="K43" s="17" t="n">
         <v>2.83</v>
       </c>
-      <c r="L43" s="14" t="n">
+      <c r="L43" s="17" t="n">
         <v>5.22</v>
       </c>
-      <c r="M43" s="14" t="n">
+      <c r="M43" s="17" t="n">
         <v>9.18</v>
       </c>
-      <c r="N43" s="14" t="n">
+      <c r="N43" s="17" t="n">
         <v>12.64</v>
       </c>
-      <c r="O43" s="14" t="n">
+      <c r="O43" s="17" t="n">
         <v>4.74</v>
       </c>
-      <c r="P43" s="14" t="n">
+      <c r="P43" s="17" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="Q43" s="14" t="n">
+      <c r="Q43" s="17" t="n">
         <v>7.3</v>
       </c>
-      <c r="R43" s="14" t="n">
+      <c r="R43" s="17" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -3687,57 +3690,57 @@
       <c r="A48" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C48" s="14" t="n">
+      <c r="C48" s="17" t="n">
         <v>10.89</v>
       </c>
-      <c r="D48" s="14" t="n">
+      <c r="D48" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E48" s="14" t="n">
+      <c r="E48" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F48" s="14" t="n">
+      <c r="F48" s="17" t="n">
         <v>24.5</v>
       </c>
-      <c r="G48" s="14" t="n">
+      <c r="G48" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="H48" s="14" t="n">
+      <c r="H48" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="I48" s="14" t="n">
+      <c r="I48" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="J48" s="14" t="n">
+      <c r="J48" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="K48" s="14" t="n">
+      <c r="K48" s="17" t="n">
         <v>12.16</v>
       </c>
-      <c r="L48" s="14" t="n">
+      <c r="L48" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="M48" s="14" t="n">
+      <c r="M48" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="N48" s="14" t="n">
+      <c r="N48" s="17" t="n">
         <v>24.2</v>
       </c>
-      <c r="O48" s="14" t="n">
+      <c r="O48" s="17" t="n">
         <v>18.43</v>
       </c>
-      <c r="P48" s="14" t="n">
+      <c r="P48" s="17" t="n">
         <v>23.24</v>
       </c>
-      <c r="Q48" s="14" t="n">
+      <c r="Q48" s="17" t="n">
         <v>20.84</v>
       </c>
-      <c r="R48" s="14" t="n">
+      <c r="R48" s="17" t="n">
         <v>20.84</v>
       </c>
     </row>
@@ -3745,57 +3748,57 @@
       <c r="A49" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="19" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C49" s="14" t="n">
+      <c r="C49" s="17" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="D49" s="14" t="n">
+      <c r="D49" s="17" t="n">
         <v>16.62</v>
       </c>
-      <c r="E49" s="14" t="n">
+      <c r="E49" s="17" t="n">
         <v>21.04</v>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="F49" s="17" t="n">
         <v>23.57</v>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="G49" s="17" t="n">
         <v>10.97</v>
       </c>
-      <c r="H49" s="14" t="n">
+      <c r="H49" s="17" t="n">
         <v>16.62</v>
       </c>
-      <c r="I49" s="14" t="n">
+      <c r="I49" s="17" t="n">
         <v>21.04</v>
       </c>
-      <c r="J49" s="14" t="n">
+      <c r="J49" s="17" t="n">
         <v>22.81</v>
       </c>
-      <c r="K49" s="14" t="n">
+      <c r="K49" s="17" t="n">
         <v>10.23</v>
       </c>
-      <c r="L49" s="14" t="n">
+      <c r="L49" s="17" t="n">
         <v>16.62</v>
       </c>
-      <c r="M49" s="14" t="n">
+      <c r="M49" s="17" t="n">
         <v>21.04</v>
       </c>
-      <c r="N49" s="14" t="n">
+      <c r="N49" s="17" t="n">
         <v>23.11</v>
       </c>
-      <c r="O49" s="14" t="n">
+      <c r="O49" s="17" t="n">
         <v>15.34</v>
       </c>
-      <c r="P49" s="14" t="n">
+      <c r="P49" s="17" t="n">
         <v>21.45</v>
       </c>
-      <c r="Q49" s="14" t="n">
+      <c r="Q49" s="17" t="n">
         <v>18.39</v>
       </c>
-      <c r="R49" s="14" t="n">
+      <c r="R49" s="17" t="n">
         <v>20.84</v>
       </c>
     </row>
@@ -3803,57 +3806,57 @@
       <c r="A50" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C50" s="14" t="n">
+      <c r="C50" s="17" t="n">
         <v>7.3</v>
       </c>
-      <c r="D50" s="14" t="n">
+      <c r="D50" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="E50" s="14" t="n">
+      <c r="E50" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="F50" s="14" t="n">
+      <c r="F50" s="17" t="n">
         <v>22.64</v>
       </c>
-      <c r="G50" s="14" t="n">
+      <c r="G50" s="17" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="H50" s="14" t="n">
+      <c r="H50" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="I50" s="14" t="n">
+      <c r="I50" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="J50" s="14" t="n">
+      <c r="J50" s="17" t="n">
         <v>21.62</v>
       </c>
-      <c r="K50" s="14" t="n">
+      <c r="K50" s="17" t="n">
         <v>8.289999999999999</v>
       </c>
-      <c r="L50" s="14" t="n">
+      <c r="L50" s="17" t="n">
         <v>13.24</v>
       </c>
-      <c r="M50" s="14" t="n">
+      <c r="M50" s="17" t="n">
         <v>19.09</v>
       </c>
-      <c r="N50" s="14" t="n">
+      <c r="N50" s="17" t="n">
         <v>22.03</v>
       </c>
-      <c r="O50" s="14" t="n">
+      <c r="O50" s="17" t="n">
         <v>12.25</v>
       </c>
-      <c r="P50" s="14" t="n">
+      <c r="P50" s="17" t="n">
         <v>19.68</v>
       </c>
-      <c r="Q50" s="14" t="n">
+      <c r="Q50" s="17" t="n">
         <v>15.96</v>
       </c>
-      <c r="R50" s="14" t="n">
+      <c r="R50" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3861,57 +3864,57 @@
       <c r="A51" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="17" t="n">
         <v>5.66</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="E51" s="14" t="n">
+      <c r="E51" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="F51" s="17" t="n">
         <v>19.68</v>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="G51" s="17" t="n">
         <v>7.03</v>
       </c>
-      <c r="H51" s="14" t="n">
+      <c r="H51" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="I51" s="14" t="n">
+      <c r="I51" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="J51" s="17" t="n">
         <v>18.85</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="K51" s="17" t="n">
         <v>6.48</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="L51" s="17" t="n">
         <v>11.9</v>
       </c>
-      <c r="M51" s="14" t="n">
+      <c r="M51" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="N51" s="14" t="n">
+      <c r="N51" s="17" t="n">
         <v>19.18</v>
       </c>
-      <c r="O51" s="14" t="n">
+      <c r="O51" s="17" t="n">
         <v>10.82</v>
       </c>
-      <c r="P51" s="14" t="n">
+      <c r="P51" s="17" t="n">
         <v>17.32</v>
       </c>
-      <c r="Q51" s="14" t="n">
+      <c r="Q51" s="17" t="n">
         <v>14.07</v>
       </c>
-      <c r="R51" s="14" t="n">
+      <c r="R51" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3919,57 +3922,57 @@
       <c r="A52" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="14" t="n">
+      <c r="C52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E52" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="F52" s="14" t="n">
+      <c r="F52" s="17" t="n">
         <v>7.7</v>
       </c>
-      <c r="G52" s="14" t="n">
+      <c r="G52" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="H52" s="14" t="n">
+      <c r="H52" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="I52" s="14" t="n">
+      <c r="I52" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="J52" s="14" t="n">
+      <c r="J52" s="17" t="n">
         <v>6.11</v>
       </c>
-      <c r="K52" s="14" t="n">
+      <c r="K52" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="L52" s="14" t="n">
+      <c r="L52" s="17" t="n">
         <v>1.1</v>
       </c>
-      <c r="M52" s="14" t="n">
+      <c r="M52" s="17" t="n">
         <v>2.64</v>
       </c>
-      <c r="N52" s="14" t="n">
+      <c r="N52" s="17" t="n">
         <v>6.75</v>
       </c>
-      <c r="O52" s="14" t="n">
+      <c r="O52" s="17" t="n">
         <v>0.89</v>
       </c>
-      <c r="P52" s="14" t="n">
+      <c r="P52" s="17" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q52" s="14" t="n">
+      <c r="Q52" s="17" t="n">
         <v>2.17</v>
       </c>
-      <c r="R52" s="14" t="n">
+      <c r="R52" s="17" t="n">
         <v>15.96</v>
       </c>
     </row>
@@ -3977,57 +3980,57 @@
       <c r="A53" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C53" s="14" t="n">
+      <c r="C53" s="17" t="n">
         <v>6.76</v>
       </c>
-      <c r="D53" s="14" t="n">
+      <c r="D53" s="17" t="n">
         <v>12.72</v>
       </c>
-      <c r="E53" s="14" t="n">
+      <c r="E53" s="17" t="n">
         <v>17.69</v>
       </c>
-      <c r="F53" s="14" t="n">
+      <c r="F53" s="17" t="n">
         <v>20.03</v>
       </c>
-      <c r="G53" s="14" t="n">
+      <c r="G53" s="17" t="n">
         <v>8.06</v>
       </c>
-      <c r="H53" s="14" t="n">
+      <c r="H53" s="17" t="n">
         <v>12.72</v>
       </c>
-      <c r="I53" s="14" t="n">
+      <c r="I53" s="17" t="n">
         <v>17.69</v>
       </c>
-      <c r="J53" s="14" t="n">
+      <c r="J53" s="17" t="n">
         <v>19.37</v>
       </c>
-      <c r="K53" s="14" t="n">
+      <c r="K53" s="17" t="n">
         <v>7.54</v>
       </c>
-      <c r="L53" s="14" t="n">
+      <c r="L53" s="17" t="n">
         <v>12.72</v>
       </c>
-      <c r="M53" s="14" t="n">
+      <c r="M53" s="17" t="n">
         <v>17.69</v>
       </c>
-      <c r="N53" s="14" t="n">
+      <c r="N53" s="17" t="n">
         <v>19.63</v>
       </c>
-      <c r="O53" s="14" t="n">
+      <c r="O53" s="17" t="n">
         <v>11.68</v>
       </c>
-      <c r="P53" s="14" t="n">
+      <c r="P53" s="17" t="n">
         <v>18.08</v>
       </c>
-      <c r="Q53" s="14" t="n">
+      <c r="Q53" s="17" t="n">
         <v>14.88</v>
       </c>
-      <c r="R53" s="14" t="n">
+      <c r="R53" s="17" t="n">
         <v>14.88</v>
       </c>
     </row>
@@ -4035,57 +4038,57 @@
       <c r="A54" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C54" s="14" t="n">
+      <c r="C54" s="17" t="n">
         <v>4.83</v>
       </c>
-      <c r="D54" s="14" t="n">
+      <c r="D54" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="E54" s="14" t="n">
+      <c r="E54" s="17" t="n">
         <v>16.29</v>
       </c>
-      <c r="F54" s="14" t="n">
+      <c r="F54" s="17" t="n">
         <v>19.75</v>
       </c>
-      <c r="G54" s="14" t="n">
+      <c r="G54" s="17" t="n">
         <v>6.21</v>
       </c>
-      <c r="H54" s="14" t="n">
+      <c r="H54" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="I54" s="14" t="n">
+      <c r="I54" s="17" t="n">
         <v>16.29</v>
       </c>
-      <c r="J54" s="14" t="n">
+      <c r="J54" s="17" t="n">
         <v>18.73</v>
       </c>
-      <c r="K54" s="14" t="n">
+      <c r="K54" s="17" t="n">
         <v>5.66</v>
       </c>
-      <c r="L54" s="14" t="n">
+      <c r="L54" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="M54" s="14" t="n">
+      <c r="M54" s="17" t="n">
         <v>16.29</v>
       </c>
-      <c r="N54" s="14" t="n">
+      <c r="N54" s="17" t="n">
         <v>19.14</v>
       </c>
-      <c r="O54" s="14" t="n">
+      <c r="O54" s="17" t="n">
         <v>9.76</v>
       </c>
-      <c r="P54" s="14" t="n">
+      <c r="P54" s="17" t="n">
         <v>16.86</v>
       </c>
-      <c r="Q54" s="14" t="n">
+      <c r="Q54" s="17" t="n">
         <v>13.31</v>
       </c>
-      <c r="R54" s="14" t="n">
+      <c r="R54" s="17" t="n">
         <v>13.31</v>
       </c>
     </row>
@@ -4093,57 +4096,57 @@
       <c r="A55" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C55" s="14" t="n">
+      <c r="C55" s="17" t="n">
         <v>4.83</v>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="E55" s="14" t="n">
+      <c r="E55" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="F55" s="14" t="n">
+      <c r="F55" s="17" t="n">
         <v>16.94</v>
       </c>
-      <c r="G55" s="14" t="n">
+      <c r="G55" s="17" t="n">
         <v>5.97</v>
       </c>
-      <c r="H55" s="14" t="n">
+      <c r="H55" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="I55" s="14" t="n">
+      <c r="I55" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="J55" s="14" t="n">
+      <c r="J55" s="17" t="n">
         <v>15.59</v>
       </c>
-      <c r="K55" s="14" t="n">
+      <c r="K55" s="17" t="n">
         <v>5.51</v>
       </c>
-      <c r="L55" s="14" t="n">
+      <c r="L55" s="17" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="M55" s="14" t="n">
+      <c r="M55" s="17" t="n">
         <v>12.54</v>
       </c>
-      <c r="N55" s="14" t="n">
+      <c r="N55" s="17" t="n">
         <v>16.13</v>
       </c>
-      <c r="O55" s="14" t="n">
+      <c r="O55" s="17" t="n">
         <v>8.4</v>
       </c>
-      <c r="P55" s="14" t="n">
+      <c r="P55" s="17" t="n">
         <v>13.26</v>
       </c>
-      <c r="Q55" s="14" t="n">
+      <c r="Q55" s="17" t="n">
         <v>10.83</v>
       </c>
-      <c r="R55" s="14" t="n">
+      <c r="R55" s="17" t="n">
         <v>10.83</v>
       </c>
     </row>
@@ -4151,57 +4154,57 @@
       <c r="A56" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B56" s="19" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C56" s="14" t="n">
+      <c r="C56" s="17" t="n">
         <v>1.38</v>
       </c>
-      <c r="D56" s="14" t="n">
+      <c r="D56" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="E56" s="14" t="n">
+      <c r="E56" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="F56" s="14" t="n">
+      <c r="F56" s="17" t="n">
         <v>15.86</v>
       </c>
-      <c r="G56" s="14" t="n">
+      <c r="G56" s="17" t="n">
         <v>2.26</v>
       </c>
-      <c r="H56" s="14" t="n">
+      <c r="H56" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="I56" s="14" t="n">
+      <c r="I56" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="J56" s="14" t="n">
+      <c r="J56" s="17" t="n">
         <v>14.77</v>
       </c>
-      <c r="K56" s="14" t="n">
+      <c r="K56" s="17" t="n">
         <v>1.91</v>
       </c>
-      <c r="L56" s="14" t="n">
+      <c r="L56" s="17" t="n">
         <v>6.05</v>
       </c>
-      <c r="M56" s="14" t="n">
+      <c r="M56" s="17" t="n">
         <v>12.1</v>
       </c>
-      <c r="N56" s="14" t="n">
+      <c r="N56" s="17" t="n">
         <v>15.21</v>
       </c>
-      <c r="O56" s="14" t="n">
+      <c r="O56" s="17" t="n">
         <v>5.22</v>
       </c>
-      <c r="P56" s="14" t="n">
+      <c r="P56" s="17" t="n">
         <v>12.72</v>
       </c>
-      <c r="Q56" s="14" t="n">
+      <c r="Q56" s="17" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="R56" s="14" t="n">
+      <c r="R56" s="17" t="n">
         <v>10.83</v>
       </c>
     </row>
@@ -4209,57 +4212,57 @@
       <c r="A57" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="19" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C57" s="14" t="n">
+      <c r="C57" s="17" t="n">
         <v>2.35</v>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D57" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E57" s="14" t="n">
+      <c r="E57" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="F57" s="14" t="n">
+      <c r="F57" s="17" t="n">
         <v>11.24</v>
       </c>
-      <c r="G57" s="14" t="n">
+      <c r="G57" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="14" t="n">
+      <c r="H57" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="14" t="n">
+      <c r="I57" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="J57" s="14" t="n">
+      <c r="J57" s="17" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="K57" s="14" t="n">
+      <c r="K57" s="17" t="n">
         <v>2.74</v>
       </c>
-      <c r="L57" s="14" t="n">
+      <c r="L57" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="M57" s="14" t="n">
+      <c r="M57" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="N57" s="14" t="n">
+      <c r="N57" s="17" t="n">
         <v>10.23</v>
       </c>
-      <c r="O57" s="14" t="n">
+      <c r="O57" s="17" t="n">
         <v>4.55</v>
       </c>
-      <c r="P57" s="14" t="n">
+      <c r="P57" s="17" t="n">
         <v>6.85</v>
       </c>
-      <c r="Q57" s="14" t="n">
+      <c r="Q57" s="17" t="n">
         <v>5.7</v>
       </c>
-      <c r="R57" s="14" t="n">
+      <c r="R57" s="17" t="n">
         <v>5.7</v>
       </c>
     </row>
@@ -4300,9 +4303,9 @@
   <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -4310,19 +4313,19 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Нечеткий MoSCoW — итоги (коллективное решение)</t>
+          <t>Нечеткий MoSCoW - итоги (коллективное решение, метод взвешенной средней)</t>
         </is>
       </c>
     </row>
@@ -4442,54 +4445,54 @@
       <c r="A6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>11.48</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="17" t="n">
         <v>20.75</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="17" t="n">
         <v>23.75</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="17" t="n">
         <v>24.8</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="17" t="n">
         <v>13.6</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="17" t="n">
         <v>20.75</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="17" t="n">
         <v>23.75</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="17" t="n">
         <v>24.45</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="17" t="n">
         <v>12.75</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="17" t="n">
         <v>20.75</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="M6" s="17" t="n">
         <v>23.75</v>
       </c>
-      <c r="N6" s="14" t="n">
+      <c r="N6" s="17" t="n">
         <v>24.59</v>
       </c>
-      <c r="O6" s="14" t="n">
+      <c r="O6" s="17" t="n">
         <v>19.15</v>
       </c>
-      <c r="P6" s="14" t="n">
+      <c r="P6" s="17" t="n">
         <v>23.92</v>
       </c>
-      <c r="Q6" s="14" t="n">
+      <c r="Q6" s="17" t="n">
         <v>21.54</v>
       </c>
     </row>
@@ -4497,54 +4500,54 @@
       <c r="A7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>10.22</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="17" t="n">
         <v>18.39</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="17" t="n">
         <v>22.38</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="17" t="n">
         <v>24.15</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="17" t="n">
         <v>12.18</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="17" t="n">
         <v>18.39</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="17" t="n">
         <v>22.38</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="17" t="n">
         <v>23.61</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="17" t="n">
         <v>11.4</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="17" t="n">
         <v>18.39</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="17" t="n">
         <v>22.38</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="N7" s="17" t="n">
         <v>23.83</v>
       </c>
-      <c r="O7" s="14" t="n">
+      <c r="O7" s="17" t="n">
         <v>16.99</v>
       </c>
-      <c r="P7" s="14" t="n">
+      <c r="P7" s="17" t="n">
         <v>22.67</v>
       </c>
-      <c r="Q7" s="14" t="n">
+      <c r="Q7" s="17" t="n">
         <v>19.83</v>
       </c>
     </row>
@@ -4552,54 +4555,54 @@
       <c r="A8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="17" t="n">
         <v>7.34</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="17" t="n">
         <v>12.98</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="17" t="n">
         <v>19.26</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="17" t="n">
         <v>22.66</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="17" t="n">
         <v>8.949999999999999</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="17" t="n">
         <v>12.98</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="17" t="n">
         <v>19.26</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="17" t="n">
         <v>21.72</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="17" t="n">
         <v>8.31</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="17" t="n">
         <v>12.98</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="17" t="n">
         <v>19.26</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="N8" s="17" t="n">
         <v>22.1</v>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="17" t="n">
         <v>12.05</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="17" t="n">
         <v>19.83</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="Q8" s="17" t="n">
         <v>15.94</v>
       </c>
     </row>
@@ -4607,54 +4610,54 @@
       <c r="A9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="17" t="n">
         <v>6.72</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="17" t="n">
         <v>12.33</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="17" t="n">
         <v>15.94</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="17" t="n">
         <v>18.75</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="17" t="n">
         <v>8.01</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="17" t="n">
         <v>12.33</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="17" t="n">
         <v>15.94</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="17" t="n">
         <v>17.9</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="17" t="n">
         <v>7.49</v>
       </c>
-      <c r="L9" s="14" t="n">
+      <c r="L9" s="17" t="n">
         <v>12.33</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="17" t="n">
         <v>15.94</v>
       </c>
-      <c r="N9" s="14" t="n">
+      <c r="N9" s="17" t="n">
         <v>18.24</v>
       </c>
-      <c r="O9" s="14" t="n">
+      <c r="O9" s="17" t="n">
         <v>11.36</v>
       </c>
-      <c r="P9" s="14" t="n">
+      <c r="P9" s="17" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q9" s="14" t="n">
+      <c r="Q9" s="17" t="n">
         <v>13.88</v>
       </c>
     </row>
@@ -4662,54 +4665,54 @@
       <c r="A10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="17" t="n">
         <v>5.24</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="17" t="n">
         <v>11.57</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="17" t="n">
         <v>16.59</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="17" t="n">
         <v>19.13</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="17" t="n">
         <v>6.56</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="17" t="n">
         <v>11.57</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="17" t="n">
         <v>16.59</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="17" t="n">
         <v>18.4</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="17" t="n">
         <v>6.03</v>
       </c>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="17" t="n">
         <v>11.57</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="17" t="n">
         <v>16.59</v>
       </c>
-      <c r="N10" s="14" t="n">
+      <c r="N10" s="17" t="n">
         <v>18.69</v>
       </c>
-      <c r="O10" s="14" t="n">
+      <c r="O10" s="17" t="n">
         <v>10.46</v>
       </c>
-      <c r="P10" s="14" t="n">
+      <c r="P10" s="17" t="n">
         <v>17.01</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="Q10" s="17" t="n">
         <v>13.74</v>
       </c>
     </row>
@@ -4717,54 +4720,54 @@
       <c r="A11" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>5.32</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="17" t="n">
         <v>10.58</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="17" t="n">
         <v>16.88</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="17" t="n">
         <v>20.34</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="17" t="n">
         <v>6.67</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="17" t="n">
         <v>10.58</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="17" t="n">
         <v>16.88</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="17" t="n">
         <v>19.37</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="17" t="n">
         <v>6.13</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L11" s="17" t="n">
         <v>10.58</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="17" t="n">
         <v>16.88</v>
       </c>
-      <c r="N11" s="14" t="n">
+      <c r="N11" s="17" t="n">
         <v>19.76</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="17" t="n">
         <v>9.69</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="17" t="n">
         <v>17.46</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="17" t="n">
         <v>13.57</v>
       </c>
     </row>
@@ -4772,54 +4775,54 @@
       <c r="A12" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>4.87</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="17" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="17" t="n">
         <v>12.71</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="17" t="n">
         <v>16.96</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="17" t="n">
         <v>5.97</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="17" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="17" t="n">
         <v>12.71</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="17" t="n">
         <v>15.69</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="17" t="n">
         <v>5.53</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L12" s="17" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="17" t="n">
         <v>12.71</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N12" s="17" t="n">
         <v>16.2</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="17" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="17" t="n">
         <v>13.41</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="17" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -4827,54 +4830,54 @@
       <c r="A13" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>0.96</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="17" t="n">
         <v>5.72</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="17" t="n">
         <v>11.84</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="17" t="n">
         <v>15.31</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="17" t="n">
         <v>1.79</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="17" t="n">
         <v>5.72</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="17" t="n">
         <v>11.84</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="17" t="n">
         <v>14.32</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="17" t="n">
         <v>1.46</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="L13" s="17" t="n">
         <v>5.72</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="17" t="n">
         <v>11.84</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="17" t="n">
         <v>14.72</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="17" t="n">
         <v>4.87</v>
       </c>
-      <c r="P13" s="14" t="n">
+      <c r="P13" s="17" t="n">
         <v>12.42</v>
       </c>
-      <c r="Q13" s="14" t="n">
+      <c r="Q13" s="17" t="n">
         <v>8.640000000000001</v>
       </c>
     </row>
@@ -4882,54 +4885,54 @@
       <c r="A14" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>2.42</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="17" t="n">
         <v>4.81</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="17" t="n">
         <v>7.11</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="17" t="n">
         <v>11.91</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="17" t="n">
         <v>3.01</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="17" t="n">
         <v>4.81</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="17" t="n">
         <v>7.11</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="17" t="n">
         <v>10.42</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="17" t="n">
         <v>2.77</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="17" t="n">
         <v>4.81</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="17" t="n">
         <v>7.11</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N14" s="17" t="n">
         <v>11.02</v>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O14" s="17" t="n">
         <v>4.4</v>
       </c>
-      <c r="P14" s="14" t="n">
+      <c r="P14" s="17" t="n">
         <v>7.89</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="17" t="n">
         <v>6.14</v>
       </c>
     </row>
@@ -4937,54 +4940,54 @@
       <c r="A15" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14" t="n">
+      <c r="C15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <v>0.77</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="17" t="n">
         <v>1.85</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="17" t="n">
         <v>7.07</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="17" t="n">
         <v>0.77</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="17" t="n">
         <v>1.85</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="17" t="n">
         <v>5.41</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="L15" s="17" t="n">
         <v>0.77</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M15" s="17" t="n">
         <v>1.85</v>
       </c>
-      <c r="N15" s="14" t="n">
+      <c r="N15" s="17" t="n">
         <v>6.07</v>
       </c>
-      <c r="O15" s="14" t="n">
+      <c r="O15" s="17" t="n">
         <v>0.62</v>
       </c>
-      <c r="P15" s="14" t="n">
+      <c r="P15" s="17" t="n">
         <v>2.69</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="Q15" s="17" t="n">
         <v>1.66</v>
       </c>
     </row>
@@ -5023,15 +5026,15 @@
       <c r="A19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>21.54</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>21.54</v>
       </c>
     </row>
@@ -5039,15 +5042,15 @@
       <c r="A20" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>19.83</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>21.54</v>
       </c>
     </row>
@@ -5055,15 +5058,15 @@
       <c r="A21" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>15.94</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>15.94</v>
       </c>
     </row>
@@ -5071,15 +5074,15 @@
       <c r="A22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>13.74</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>15.94</v>
       </c>
     </row>
@@ -5087,15 +5090,15 @@
       <c r="A23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>1.66</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>15.94</v>
       </c>
     </row>
@@ -5103,15 +5106,15 @@
       <c r="A24" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>13.88</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>13.88</v>
       </c>
     </row>
@@ -5119,15 +5122,15 @@
       <c r="A25" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>13.57</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>13.57</v>
       </c>
     </row>
@@ -5135,15 +5138,15 @@
       <c r="A26" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>10.8</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -5151,15 +5154,15 @@
       <c r="A27" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -5167,15 +5170,15 @@
       <c r="A28" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>6.14</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>6.14</v>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
@@ -2131,7 +2131,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Параметры дефаззификации</t>
+          <t>2) Гиперпараметры модели</t>
         </is>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_Fuzzy MoSCoW_взвешенные средние.xlsx
@@ -2131,7 +2131,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Гиперпараметры модели</t>
+          <t>2) Параметры модели</t>
         </is>
       </c>
     </row>
